--- a/data/trans_orig/P04C05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023</t>
+          <t>Población según si dispone de refrigeración por aire acondicionado mediante aparatos fijos en la vivienda en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71094</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>32111</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57973</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77401</t>
+          <t>78006</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>119944</t>
+          <t>118414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>240111</t>
+          <t>241040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>271089</t>
+          <t>271504</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>229460</t>
+          <t>230723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>255940</t>
+          <t>255817</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>479823</t>
+          <t>481956</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>522176</t>
+          <t>521566</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>231734</t>
+          <t>228202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291707</t>
+          <t>288471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280152</t>
+          <t>279735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>321860</t>
+          <t>322673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>522991</t>
+          <t>520317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>595922</t>
+          <t>595052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>224715</t>
+          <t>226870</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>284748</t>
+          <t>287721</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>192067</t>
+          <t>191197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233230</t>
+          <t>234439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433487</t>
+          <t>435373</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>506541</t>
+          <t>508276</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,19%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39789</t>
+          <t>39882</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66677</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50171</t>
+          <t>51074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75290</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>96834</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131643</t>
+          <t>132504</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10326</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>243707</t>
+          <t>244805</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271481</t>
+          <t>271059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271289</t>
+          <t>271386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>296122</t>
+          <t>295574</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525240</t>
+          <t>524370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>560611</t>
+          <t>561503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97706</t>
+          <t>97497</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>198673</t>
+          <t>194779</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>340622</t>
+          <t>334063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>309720</t>
+          <t>314239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480935</t>
+          <t>487340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14747</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>21611</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166481</t>
+          <t>165430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>208640</t>
+          <t>208326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>128889</t>
+          <t>134152</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>269555</t>
+          <t>273490</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295954</t>
+          <t>290612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>462426</t>
+          <t>457808</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,21%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42065</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63274</t>
+          <t>63074</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34067</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81029</t>
+          <t>79885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137552</t>
+          <t>138839</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>8588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16892</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>109737</t>
+          <t>110525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132157</t>
+          <t>131542</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169791</t>
+          <t>168102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222109</t>
+          <t>219677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>289678</t>
+          <t>288936</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>350883</t>
+          <t>351959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58015</t>
+          <t>58432</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25571</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41761</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66555</t>
+          <t>66206</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>93934</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>354</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>8384</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209995</t>
+          <t>209484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232531</t>
+          <t>232455</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>212491</t>
+          <t>211420</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>228963</t>
+          <t>229170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>428443</t>
+          <t>427136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>456361</t>
+          <t>456536</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,68%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>149318</t>
+          <t>152603</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202015</t>
+          <t>204998</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>83461</t>
+          <t>86366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>259251</t>
+          <t>260846</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>236871</t>
+          <t>231809</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>441046</t>
+          <t>437558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14110</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32486</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>407955</t>
+          <t>406172</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>459966</t>
+          <t>459344</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>574585</t>
+          <t>574723</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757249</t>
+          <t>754595</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1003799</t>
+          <t>1005562</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1218469</t>
+          <t>1223787</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,33%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>10169</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37318</t>
+          <t>38524</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43551</t>
+          <t>40228</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>26129</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>65182</t>
+          <t>64664</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>19769</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>881975</t>
+          <t>880764</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>916013</t>
+          <t>914974</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>669919</t>
+          <t>672198</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>699506</t>
+          <t>699215</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1568201</t>
+          <t>1568166</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1612274</t>
+          <t>1612260</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>617313</t>
+          <t>587270</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>857821</t>
+          <t>860060</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>810917</t>
+          <t>821691</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1115023</t>
+          <t>1121098</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1517268</t>
+          <t>1517165</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1917868</t>
+          <t>1916964</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>56234</t>
+          <t>55535</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23068</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41071</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>58432</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>90684</t>
+          <t>91208</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2555774</t>
+          <t>2552235</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2806529</t>
+          <t>2841414</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2562267</t>
+          <t>2554007</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2873706</t>
+          <t>2859473</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5180703</t>
+          <t>5168614</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5593033</t>
+          <t>5576810</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04C05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P04C05_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53481</t>
+          <t>74413</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>60476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>91109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42036</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>46161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>71851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>95516</t>
+          <t>131523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78006</t>
+          <t>112470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>118414</t>
+          <t>149954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>827</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1601</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>8194</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>257795</t>
+          <t>243606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>241040</t>
+          <t>226309</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>271504</t>
+          <t>257446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>245998</t>
+          <t>256635</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>230723</t>
+          <t>242419</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>255817</t>
+          <t>267584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>503792</t>
+          <t>500240</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>481956</t>
+          <t>481319</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>521566</t>
+          <t>518661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>81,69%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>259024</t>
+          <t>264949</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>228202</t>
+          <t>237281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>288471</t>
+          <t>295804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299959</t>
+          <t>317711</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279735</t>
+          <t>298145</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322673</t>
+          <t>337197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>558983</t>
+          <t>582660</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>520317</t>
+          <t>542615</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>595052</t>
+          <t>618266</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9981</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4107</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>256528</t>
+          <t>262954</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226870</t>
+          <t>233271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>287721</t>
+          <t>291686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>213645</t>
+          <t>227419</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>191197</t>
+          <t>207347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234439</t>
+          <t>246772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>470173</t>
+          <t>490374</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435373</t>
+          <t>455579</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>508276</t>
+          <t>530364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>51275</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65107</t>
+          <t>65590</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>61987</t>
+          <t>65880</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51074</t>
+          <t>54537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74911</t>
+          <t>79776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>117771</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96834</t>
+          <t>100814</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132504</t>
+          <t>135585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4169</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10326</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>259586</t>
+          <t>259010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244805</t>
+          <t>245097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271059</t>
+          <t>271072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>284323</t>
+          <t>287581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>271386</t>
+          <t>273840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>295574</t>
+          <t>299936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>543909</t>
+          <t>546592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>524370</t>
+          <t>528200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>561503</t>
+          <t>563264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>315031</t>
+          <t>314908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>664158</t>
+          <t>671289</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>118324</t>
+          <t>162315</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97497</t>
+          <t>137629</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140182</t>
+          <t>189913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>251451</t>
+          <t>208720</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194779</t>
+          <t>189451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>334063</t>
+          <t>228669</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>369775</t>
+          <t>371034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314239</t>
+          <t>336473</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>487340</t>
+          <t>401343</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14636</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>187194</t>
+          <t>202807</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>165430</t>
+          <t>175595</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>208326</t>
+          <t>228214</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>216780</t>
+          <t>204440</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>134152</t>
+          <t>185004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>273490</t>
+          <t>224548</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>403973</t>
+          <t>407247</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>290612</t>
+          <t>376769</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>457808</t>
+          <t>443482</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>55,97%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>473951</t>
+          <t>419182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>473951</t>
+          <t>419182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>473951</t>
+          <t>419182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>786507</t>
+          <t>792327</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786507</t>
+          <t>792327</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>786507</t>
+          <t>792327</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>52399</t>
+          <t>58785</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42391</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63074</t>
+          <t>71081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>64962</t>
+          <t>68897</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36524</t>
+          <t>59089</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84834</t>
+          <t>80382</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>117361</t>
+          <t>127682</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79885</t>
+          <t>114673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>138839</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11864</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>13047</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5414</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16444</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>121550</t>
+          <t>139101</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>110525</t>
+          <t>126103</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131542</t>
+          <t>150158</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>189072</t>
+          <t>154752</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168102</t>
+          <t>143941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219677</t>
+          <t>165771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>310622</t>
+          <t>293852</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>288936</t>
+          <t>277981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>351959</t>
+          <t>308978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>46269</t>
+          <t>50198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35752</t>
+          <t>41186</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>58432</t>
+          <t>62054</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32740</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>27645</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42124</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>79009</t>
+          <t>85437</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66206</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,9%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5534</t>
+          <t>7391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>13075</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>221811</t>
+          <t>217054</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>209484</t>
+          <t>205904</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232455</t>
+          <t>227529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>221668</t>
+          <t>225034</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>211420</t>
+          <t>215925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>229170</t>
+          <t>233031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>443480</t>
+          <t>442088</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>427136</t>
+          <t>424836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>456536</t>
+          <t>455880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>85,3%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>175378</t>
+          <t>213217</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152603</t>
+          <t>185351</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204998</t>
+          <t>242366</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>190526</t>
+          <t>239733</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86366</t>
+          <t>216901</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>260846</t>
+          <t>264470</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>365904</t>
+          <t>452949</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>418219</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>437558</t>
+          <t>492937</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>12665</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>22868</t>
+          <t>26464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>13408</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>43365</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>435098</t>
+          <t>488166</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>406172</t>
+          <t>458684</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>459344</t>
+          <t>516958</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>646920</t>
+          <t>515003</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>574723</t>
+          <t>489958</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>754595</t>
+          <t>537861</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1082018</t>
+          <t>1003169</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1005562</t>
+          <t>964330</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1223787</t>
+          <t>1039278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>69,95%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>717567</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>717567</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>717567</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>845503</t>
+          <t>768144</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>845503</t>
+          <t>768144</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>845503</t>
+          <t>768144</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1468644</t>
+          <t>1485711</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1468644</t>
+          <t>1485711</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1468644</t>
+          <t>1485711</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>29398</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>20320</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>38524</t>
+          <t>41937</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>23055</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>15631</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40228</t>
+          <t>33140</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>64664</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>12139</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19769</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>898323</t>
+          <t>758159</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>880764</t>
+          <t>743548</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>914974</t>
+          <t>769510</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>690750</t>
+          <t>802163</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>672198</t>
+          <t>789924</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>699215</t>
+          <t>810516</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1589074</t>
+          <t>1560322</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1568166</t>
+          <t>1542219</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1612260</t>
+          <t>1574407</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>779388</t>
+          <t>905166</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>587270</t>
+          <t>846007</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>860060</t>
+          <t>964055</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>965663</t>
+          <t>1016345</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>821691</t>
+          <t>965689</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1121098</t>
+          <t>1061901</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1745051</t>
+          <t>1921511</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1517165</t>
+          <t>1850449</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1916964</t>
+          <t>2001015</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>53533</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>71789</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23068</t>
+          <t>31173</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41465</t>
+          <t>53438</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>94422</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>57314</t>
+          <t>77379</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>91208</t>
+          <t>116483</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>2637885</t>
+          <t>2570857</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2552235</t>
+          <t>2511714</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2841414</t>
+          <t>2629919</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2709156</t>
+          <t>2673028</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2554007</t>
+          <t>2624425</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2859473</t>
+          <t>2724674</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>5347041</t>
+          <t>5243886</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>5168614</t>
+          <t>5162112</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5576810</t>
+          <t>5316237</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3457659</t>
+          <t>3529556</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3706751</t>
+          <t>3730262</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7164410</t>
+          <t>7259818</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
